--- a/finance/_refresh_caribbean-mobility.xlsx
+++ b/finance/_refresh_caribbean-mobility.xlsx
@@ -1311,7 +1311,7 @@
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>Cap on revenue sailings/day — MID headline duty cycle; thin=12 / full=18 bookends in _utilization_scenarios (Jaideep 2026-06-21).</t>
+          <t>Cap on revenue sailings/day — 15 across thin/mid/full scenarios (Jaideep 2026-06-21).</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
         <v>0.7</v>
       </c>
       <c r="C33" s="19" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>

--- a/finance/_refresh_caribbean-mobility.xlsx
+++ b/finance/_refresh_caribbean-mobility.xlsx
@@ -27,23 +27,23 @@
     <definedName name="dwell_min">'Assumptions'!$B$18</definedName>
     <definedName name="max_tpd">'Assumptions'!$B$19</definedName>
     <definedName name="crew_factor">'Assumptions'!$B$20</definedName>
-    <definedName name="ins_pct">'Assumptions'!$B$21</definedName>
-    <definedName name="charge_berth">'Assumptions'!$B$22</definedName>
-    <definedName name="mech_uptime">'Assumptions'!$B$23</definedName>
-    <definedName name="capture">'Assumptions'!$B$24</definedName>
-    <definedName name="capture_captive">'Assumptions'!$B$25</definedName>
-    <definedName name="discount">'Assumptions'!$B$26</definedName>
-    <definedName name="diesel_co2pg">'Assumptions'!$B$27</definedName>
-    <definedName name="load_thin">'Assumptions'!$B$31</definedName>
-    <definedName name="revleg_thin">'Assumptions'!$C$31</definedName>
-    <definedName name="load_mid">'Assumptions'!$B$32</definedName>
-    <definedName name="revleg_mid">'Assumptions'!$C$32</definedName>
-    <definedName name="load_full">'Assumptions'!$B$33</definedName>
-    <definedName name="revleg_full">'Assumptions'!$C$33</definedName>
-    <definedName name="band_tbl">'Assumptions'!$A$31:$C$33</definedName>
-    <definedName name="scenario">'Assumptions'!$B$35</definedName>
-    <definedName name="load_sel">'Assumptions'!$B$36</definedName>
-    <definedName name="revleg_sel">'Assumptions'!$B$37</definedName>
+    <definedName name="mech_uptime">'Assumptions'!$B$21</definedName>
+    <definedName name="capture">'Assumptions'!$B$22</definedName>
+    <definedName name="capture_captive">'Assumptions'!$B$23</definedName>
+    <definedName name="discount">'Assumptions'!$B$24</definedName>
+    <definedName name="diesel_co2pg">'Assumptions'!$B$25</definedName>
+    <definedName name="ins_pct">'Assumptions'!$B$29</definedName>
+    <definedName name="charge_berth">'Assumptions'!$B$30</definedName>
+    <definedName name="load_thin">'Assumptions'!$B$34</definedName>
+    <definedName name="revleg_thin">'Assumptions'!$C$34</definedName>
+    <definedName name="load_mid">'Assumptions'!$B$35</definedName>
+    <definedName name="revleg_mid">'Assumptions'!$C$35</definedName>
+    <definedName name="load_full">'Assumptions'!$B$36</definedName>
+    <definedName name="revleg_full">'Assumptions'!$C$36</definedName>
+    <definedName name="band_tbl">'Assumptions'!$A$34:$C$36</definedName>
+    <definedName name="scenario">'Assumptions'!$B$38</definedName>
+    <definedName name="load_sel">'Assumptions'!$B$39</definedName>
+    <definedName name="revleg_sel">'Assumptions'!$B$40</definedName>
     <definedName name="country_opex">'Country opex'!$A$4:$G$8</definedName>
     <definedName name="som_floor_fleet">'Corridor economics'!$D$14</definedName>
     <definedName name="som_floor_rev">'Corridor economics'!$E$14</definedName>
@@ -686,7 +686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B27"/>
+  <dimension ref="B2:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -765,84 +765,143 @@
     <row r="14">
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>EBITDA  = REVENUE − OPEX   (energy + captain + marina/overhead + maintenance)</t>
+          <t>EBITDA  = REVENUE − OPEX</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    OPEX = energy + crew + berth/port admin + maintenance + vessel insurance + fast-charge berth</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>PAYBACK = vessel CAPEX ÷ EBITDA</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="2" t="inlineStr"/>
-    </row>
     <row r="17">
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>From demand pool to fleet &amp; market size</t>
-        </is>
-      </c>
+      <c r="B17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Navier serviceable rides/yr = corridor demand pool × capture rate (10% on contested corridors; ~90% on captive sole-operator transfer legs — see the per-row Capture % column)</t>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>OPEX lines (per boat, per year — no double-counting)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Vessels supported = FLOOR(Navier rides/yr ÷ pax/yr per boat);  Market rev = vessels × rev/boat. The 'Market sizing' tab rolls these up into the SOM → SAM → TAM ladder.</t>
+          <t>Energy — variable propulsion cost: kWh on revenue sailings × local $/kWh (Country opex tab). Excludes utility demand charges.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Crew — fully-loaded captain + relief: local captain wage × crew FTE factor (Country opex + Assumptions).</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>The scenario toggle (what we flex)</t>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Berth &amp; port admin — fixed annual berth, port fees, and local marine admin (Country opex tab). Excludes vessel H&amp;M+P&amp;I and fast-charge infrastructure.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>'Corridor economics' has a SCENARIO cell = THIN / MID / FULL. It flexes two levers: load factor (how full the boat is) and revenue-leg factor (how many legs earn full fare). MID is the headline. Change that one cell and the whole model recomputes. The right-hand Payback THIN/MID/FULL columns always show all three at once.</t>
+          <t>Maintenance — vessel annual maintenance reserve (Assumptions tab).</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Vessel insurance — commercial H&amp;M + P&amp;I as % of regional CAPEX (Assumptions % × Country opex CAPEX column).</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Fast-charge berth — dedicated fast-charge berth slot + utility demand charges (Assumptions default; overridable per market). Separate from per-kWh energy and berth/port admin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>From demand pool to fleet &amp; market size</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Navier serviceable rides/yr = corridor demand pool × capture rate (10% on contested corridors; ~90% on captive sole-operator transfer legs — see the per-row Capture % column)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Vessels supported = FLOOR(Navier rides/yr ÷ pax/yr per boat);  Market rev = vessels × rev/boat. The 'Market sizing' tab rolls these up into the SOM → SAM → TAM ladder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>The scenario toggle (what we flex)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>'Corridor economics' has a SCENARIO cell = THIN / MID / FULL. It flexes load factor (occupancy) and revenue-leg factor (share of legs that earn full fare). Max trips/day is fixed across all three bands (see Assumptions). MID is the headline. Change SCENARIO and the whole model recomputes. Payback THIN/MID/FULL columns always show all three at once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>Colour &amp; provenance legend</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="6" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">   Yellow = INPUTS you can change (fare, distance, demand, weather).</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="7" t="inlineStr">
+    <row r="35">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">   Green  = COMPUTED by formula.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="2" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   Every fare &amp; demand figure carries a Source tier (T1 official → T5 modeled) + Confidence (high/med/low). Null beats a wrong number: no published pool → blank, not a guess.</t>
         </is>
@@ -859,7 +918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1348,11 +1407,11 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>Insurance (% of capex/yr)</t>
+          <t>Mechanical uptime</t>
         </is>
       </c>
       <c r="B21" s="17" t="n">
-        <v>0.025</v>
+        <v>0.75</v>
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
@@ -1361,7 +1420,7 @@
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
@@ -1371,29 +1430,25 @@
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>H&amp;M + P&amp;I for a commercial passenger vessel ~2.5%/yr of capex; scales with regional capex overrides (Jaideep 2026-06-19).</t>
+          <t>Blade luxury aviation ~75-80% reliability uptime</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>Charging &amp; berth (additional to marina+energy)</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="n">
-        <v>18000</v>
+          <t>Navier capture rate</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n">
+        <v>0.1</v>
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>USD/yr</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
+          <t>frac</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr"/>
       <c r="E22" s="13" t="inlineStr">
         <is>
           <t>med</t>
@@ -1401,29 +1456,25 @@
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>Dedicated fast-charge berth + demand charges, ADDITIONAL to marina overhead and energy (Jaideep 2026-06-19). L3-overridable.</t>
+          <t>Navier wins ~10% of a CONTESTED corridor demand pool (locked). Captive sole-operator transfer legs (captive:true / luxury_charter / hospitality archetypes) carry the captive rate instead — see per-row Capture %.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>Mechanical uptime</t>
+          <t>Captive capture rate (A′ corridors)</t>
         </is>
       </c>
       <c r="B23" s="17" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
           <t>frac</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
+      <c r="D23" s="13" t="inlineStr"/>
       <c r="E23" s="13" t="inlineStr">
         <is>
           <t>med</t>
@@ -1431,255 +1482,303 @@
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>Blade luxury aviation ~75-80% reliability uptime</t>
+          <t>Sole-operator water-access-only transfer legs (captive:true or luxury_charter/hospitality archetype): Navier IS the transfer fleet — capture ~90%. Applied per-row in the Capture % column.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>Navier capture rate</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="n">
-        <v>0.1</v>
+          <t>Discount factor (vs comparable fare)</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="n">
+        <v>1</v>
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
           <t>frac</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr"/>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>Navier wins ~10% of a CONTESTED corridor demand pool (locked). Captive sole-operator transfer legs (captive:true / luxury_charter / hospitality archetypes) carry the captive rate instead — see per-row Capture %.</t>
+          <t>Market parity — better product, not cheaper (locked).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Captive capture rate (A′ corridors)</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="n">
-        <v>0.9</v>
+          <t>Diesel CO₂ per gallon</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="n">
+        <v>10.21</v>
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
+          <t>kg/gal</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="inlineStr">
+        <is>
+          <t>US EPA: 10.21 kg CO2 per gallon marine/diesel</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>OPEX defaults  (global fallbacks — localized energy, crew, berth admin on Country opex tab)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>Conf.</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>Source / note</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>Vessel insurance — H&amp;M + P&amp;I (% of CAPEX/yr)</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
           <t>frac</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr"/>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>med</t>
         </is>
       </c>
-      <c r="F25" s="14" t="inlineStr">
-        <is>
-          <t>Sole-operator water-access-only transfer legs (captive:true or luxury_charter/hospitality archetype): Navier IS the transfer fleet — capture ~90%. Applied per-row in the Capture % column.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>Discount factor (vs comparable fare)</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="13" t="inlineStr">
-        <is>
-          <t>frac</t>
-        </is>
-      </c>
-      <c r="D26" s="13" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F26" s="14" t="inlineStr">
-        <is>
-          <t>Market parity — better product, not cheaper (locked).</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>Diesel CO₂ per gallon</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="n">
-        <v>10.21</v>
-      </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>kg/gal</t>
-        </is>
-      </c>
-      <c r="D27" s="13" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="E27" s="13" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="inlineStr">
-        <is>
-          <t>US EPA: 10.21 kg CO2 per gallon marine/diesel</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>Utilization scenarios  (the two levers we flex)</t>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>Commercial vessel H&amp;M + P&amp;I ~2.5%/yr of regional CAPEX. Separate from berth/port admin in Country opex (Jaideep 2026-06-19).. Multiplied by regional CAPEX (Country opex col G). Not included in berth/port admin.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>Fast-charge berth &amp; demand charges (global default)</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>USD/yr</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>Dedicated fast-charge berth slot + utility demand charges. Excludes per-kWh propulsion energy and berth/port admin (Jaideep 2026-06-19). L3-overridable per market.. Dedicated charge berth + utility demand charges. Excludes per-kWh propulsion energy and berth/port admin. L3-overridable per market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>Utilization scenarios  (load factor + revenue-leg factor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="B30" s="10" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>Load factor</t>
         </is>
       </c>
-      <c r="C30" s="10" t="inlineStr">
+      <c r="C33" s="10" t="inlineStr">
         <is>
           <t>Rev-leg factor</t>
         </is>
       </c>
-      <c r="D30" s="10" t="inlineStr"/>
-      <c r="E30" s="10" t="inlineStr"/>
-      <c r="F30" s="10" t="inlineStr">
+      <c r="D33" s="10" t="inlineStr"/>
+      <c r="E33" s="10" t="inlineStr"/>
+      <c r="F33" s="10" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="18" t="inlineStr">
         <is>
           <t>THIN</t>
         </is>
       </c>
-      <c r="B31" s="19" t="n">
+      <c r="B34" s="19" t="n">
         <v>0.45</v>
       </c>
-      <c r="C31" s="19" t="n">
+      <c r="C34" s="19" t="n">
         <v>0.55</v>
       </c>
-      <c r="F31" s="14" t="inlineStr">
+      <c r="F34" s="14" t="inlineStr">
         <is>
           <t>thin/one-way/seasonal corridor — conservative floor</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="18" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="B32" s="19" t="n">
+      <c r="B35" s="19" t="n">
         <v>0.55</v>
       </c>
-      <c r="C32" s="19" t="n">
+      <c r="C35" s="19" t="n">
         <v>0.65</v>
       </c>
-      <c r="F32" s="14" t="inlineStr">
+      <c r="F35" s="14" t="inlineStr">
         <is>
           <t>HEADLINE — realistic busy two-way corridor</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="18" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
         <is>
           <t>FULL</t>
         </is>
       </c>
-      <c r="B33" s="19" t="n">
+      <c r="B36" s="19" t="n">
         <v>0.7</v>
       </c>
-      <c r="C33" s="19" t="n">
+      <c r="C36" s="19" t="n">
         <v>0.75</v>
       </c>
-      <c r="F33" s="14" t="inlineStr">
+      <c r="F36" s="14" t="inlineStr">
         <is>
           <t>mature/dense corridor — optimistic ceiling</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="20" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>SCENARIO (toggle me)</t>
         </is>
       </c>
-      <c r="B35" s="21" t="inlineStr">
+      <c r="B38" s="21" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="C35" s="22" t="inlineStr">
+      <c r="C38" s="22" t="inlineStr">
         <is>
           <t>← set THIN / MID / FULL</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>Selected load factor</t>
         </is>
       </c>
-      <c r="B36" s="23">
-        <f>VLOOKUP(scenario,'Assumptions'!$A$31:$C$33,2,FALSE)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+      <c r="B39" s="23">
+        <f>VLOOKUP(scenario,'Assumptions'!$A$34:$C$36,2,FALSE)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>Selected rev-leg factor</t>
         </is>
       </c>
-      <c r="B37" s="23">
-        <f>VLOOKUP(scenario,'Assumptions'!$A$31:$C$33,3,FALSE)</f>
+      <c r="B40" s="23">
+        <f>VLOOKUP(scenario,'Assumptions'!$A$34:$C$36,3,FALSE)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A3:F3"/>
+  <mergeCells count="5">
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A3:F3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="B38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"THIN,MID,FULL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1709,7 +1808,7 @@
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>Country opex — L3 localized layer (VLOOKUP target for the engine)</t>
+          <t>Country opex — localized inputs (crew, energy, berth admin, CAPEX)</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1835,7 @@
       </c>
       <c r="E3" s="24" t="inlineStr">
         <is>
-          <t>Marina $/yr</t>
+          <t>Berth &amp; port admin $/yr</t>
         </is>
       </c>
       <c r="F3" s="24" t="inlineStr">
@@ -1751,7 +1850,7 @@
       </c>
       <c r="H3" s="24" t="inlineStr">
         <is>
-          <t>Source notes (captain | energy | marina)</t>
+          <t>Source notes (crew | energy | berth admin)</t>
         </is>
       </c>
     </row>
@@ -1944,10 +2043,10 @@
     <col width="11" customWidth="1" min="20" max="20"/>
     <col width="10" customWidth="1" min="21" max="21"/>
     <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
     <col width="9" customWidth="1" min="24" max="24"/>
-    <col width="10" customWidth="1" min="25" max="25"/>
-    <col width="11" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
     <col width="11" customWidth="1" min="27" max="27"/>
     <col width="10" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
@@ -2108,7 +2207,7 @@
       </c>
       <c r="W3" s="24" t="inlineStr">
         <is>
-          <t>Marina/yr</t>
+          <t>Berth &amp; port admin/yr</t>
         </is>
       </c>
       <c r="X3" s="24" t="inlineStr">
@@ -2118,12 +2217,12 @@
       </c>
       <c r="Y3" s="24" t="inlineStr">
         <is>
-          <t>Insurance/yr</t>
+          <t>Vessel insurance/yr</t>
         </is>
       </c>
       <c r="Z3" s="24" t="inlineStr">
         <is>
-          <t>Charge+berth/yr</t>
+          <t>Fast-charge berth/yr</t>
         </is>
       </c>
       <c r="AA3" s="24" t="inlineStr">

--- a/finance/_refresh_caribbean-mobility.xlsx
+++ b/finance/_refresh_caribbean-mobility.xlsx
@@ -179,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -315,6 +315,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2018,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2063,14 +2069,15 @@
     <col width="9" customWidth="1" min="40" max="40"/>
     <col width="13" customWidth="1" min="41" max="41"/>
     <col width="26" customWidth="1" min="42" max="42"/>
-    <col width="16" customWidth="1" min="43" max="43"/>
+    <col width="14" customWidth="1" min="43" max="43"/>
     <col width="16" customWidth="1" min="44" max="44"/>
-    <col width="9" customWidth="1" min="45" max="45"/>
+    <col width="16" customWidth="1" min="45" max="45"/>
     <col width="9" customWidth="1" min="46" max="46"/>
     <col width="9" customWidth="1" min="47" max="47"/>
     <col width="9" customWidth="1" min="48" max="48"/>
-    <col width="50" customWidth="1" min="49" max="49"/>
+    <col width="9" customWidth="1" min="49" max="49"/>
     <col width="50" customWidth="1" min="50" max="50"/>
+    <col width="50" customWidth="1" min="51" max="51"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2307,40 +2314,45 @@
       </c>
       <c r="AQ3" s="24" t="inlineStr">
         <is>
+          <t>Floor bucket (aggregate status)</t>
+        </is>
+      </c>
+      <c r="AR3" s="24" t="inlineStr">
+        <is>
           <t>Forward SAM (2030-dated; held OUT of grounded floor)</t>
         </is>
       </c>
-      <c r="AR3" s="24" t="inlineStr">
+      <c r="AS3" s="24" t="inlineStr">
         <is>
           <t>Upside tier (LB-99; held OUT of grounded floor)</t>
         </is>
       </c>
-      <c r="AS3" s="24" t="inlineStr">
+      <c r="AT3" s="24" t="inlineStr">
         <is>
           <t>Fleet ceiling (captive villas/25)</t>
         </is>
       </c>
-      <c r="AT3" s="24" t="inlineStr">
+      <c r="AU3" s="24" t="inlineStr">
         <is>
           <t>Payback THIN</t>
         </is>
       </c>
-      <c r="AU3" s="24" t="inlineStr">
+      <c r="AV3" s="24" t="inlineStr">
         <is>
           <t>Payback MID</t>
         </is>
       </c>
-      <c r="AV3" s="24" t="inlineStr">
+      <c r="AW3" s="24" t="inlineStr">
         <is>
           <t>Payback FULL</t>
         </is>
       </c>
-      <c r="AW3" s="24" t="inlineStr">
+      <c r="AX3" s="24" t="inlineStr">
         <is>
           <t>Fare source (provenance)</t>
         </is>
       </c>
-      <c r="AX3" s="24" t="inlineStr">
+      <c r="AY3" s="24" t="inlineStr">
         <is>
           <t>Demand source (provenance)</t>
         </is>
@@ -2482,7 +2494,7 @@
         <v/>
       </c>
       <c r="AL4" s="34">
-        <f>IF(OR(AG4="",R4=0),"",MIN(IF(AS4="",9.9E+99,AS4),FLOOR(AK4/R4,1)))</f>
+        <f>IF(OR(AG4="",R4=0),"",MIN(IF(AT4="",9.9E+99,AT4),FLOOR(AK4/R4,1)))</f>
         <v/>
       </c>
       <c r="AM4" s="38">
@@ -2490,7 +2502,7 @@
         <v/>
       </c>
       <c r="AN4" s="36">
-        <f>IF(OR(AG4="",R4=0),"",MIN(IF(AS4="",9.9E+99,AS4),AK4/R4))</f>
+        <f>IF(OR(AG4="",R4=0),"",MIN(IF(AT4="",9.9E+99,AT4),AK4/R4))</f>
         <v/>
       </c>
       <c r="AO4" s="38">
@@ -2498,23 +2510,28 @@
         <v/>
       </c>
       <c r="AP4" s="40" t="n"/>
-      <c r="AQ4" s="41" t="n"/>
+      <c r="AQ4" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
       <c r="AR4" s="41" t="n"/>
-      <c r="AS4" s="42" t="n"/>
-      <c r="AT4" s="43">
+      <c r="AS4" s="41" t="n"/>
+      <c r="AT4" s="42" t="n"/>
+      <c r="AU4" s="43">
         <f>IF(((S4*pax_cap*load_thin*ROUND(K4*L4*revleg_thin,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_thin,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4))&lt;=0,"",VLOOKUP(B4,country_opex,7,FALSE)/((S4*pax_cap*load_thin*ROUND(K4*L4*revleg_thin,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_thin,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4)))</f>
         <v/>
       </c>
-      <c r="AU4" s="43">
+      <c r="AV4" s="43">
         <f>IF(((S4*pax_cap*load_mid*ROUND(K4*L4*revleg_mid,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_mid,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4))&lt;=0,"",VLOOKUP(B4,country_opex,7,FALSE)/((S4*pax_cap*load_mid*ROUND(K4*L4*revleg_mid,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_mid,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4)))</f>
         <v/>
       </c>
-      <c r="AV4" s="43">
+      <c r="AW4" s="43">
         <f>IF(((S4*pax_cap*load_full*ROUND(K4*L4*revleg_full,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_full,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4))&lt;=0,"",VLOOKUP(B4,country_opex,7,FALSE)/((S4*pax_cap*load_full*ROUND(K4*L4*revleg_full,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_full,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4)))</f>
         <v/>
       </c>
-      <c r="AW4" s="44" t="n"/>
       <c r="AX4" s="44" t="n"/>
+      <c r="AY4" s="44" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="29" t="inlineStr">
@@ -2652,7 +2669,7 @@
         <v/>
       </c>
       <c r="AL5" s="34">
-        <f>IF(OR(AG5="",R5=0),"",MIN(IF(AS5="",9.9E+99,AS5),FLOOR(AK5/R5,1)))</f>
+        <f>IF(OR(AG5="",R5=0),"",MIN(IF(AT5="",9.9E+99,AT5),FLOOR(AK5/R5,1)))</f>
         <v/>
       </c>
       <c r="AM5" s="38">
@@ -2660,7 +2677,7 @@
         <v/>
       </c>
       <c r="AN5" s="36">
-        <f>IF(OR(AG5="",R5=0),"",MIN(IF(AS5="",9.9E+99,AS5),AK5/R5))</f>
+        <f>IF(OR(AG5="",R5=0),"",MIN(IF(AT5="",9.9E+99,AT5),AK5/R5))</f>
         <v/>
       </c>
       <c r="AO5" s="38">
@@ -2668,23 +2685,28 @@
         <v/>
       </c>
       <c r="AP5" s="40" t="n"/>
-      <c r="AQ5" s="41" t="n"/>
+      <c r="AQ5" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
       <c r="AR5" s="41" t="n"/>
-      <c r="AS5" s="42" t="n"/>
-      <c r="AT5" s="43">
+      <c r="AS5" s="41" t="n"/>
+      <c r="AT5" s="42" t="n"/>
+      <c r="AU5" s="43">
         <f>IF(((S5*pax_cap*load_thin*ROUND(K5*L5*revleg_thin,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_thin,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5))&lt;=0,"",VLOOKUP(B5,country_opex,7,FALSE)/((S5*pax_cap*load_thin*ROUND(K5*L5*revleg_thin,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_thin,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5)))</f>
         <v/>
       </c>
-      <c r="AU5" s="43">
+      <c r="AV5" s="43">
         <f>IF(((S5*pax_cap*load_mid*ROUND(K5*L5*revleg_mid,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_mid,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5))&lt;=0,"",VLOOKUP(B5,country_opex,7,FALSE)/((S5*pax_cap*load_mid*ROUND(K5*L5*revleg_mid,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_mid,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5)))</f>
         <v/>
       </c>
-      <c r="AV5" s="43">
+      <c r="AW5" s="43">
         <f>IF(((S5*pax_cap*load_full*ROUND(K5*L5*revleg_full,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_full,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5))&lt;=0,"",VLOOKUP(B5,country_opex,7,FALSE)/((S5*pax_cap*load_full*ROUND(K5*L5*revleg_full,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_full,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5)))</f>
         <v/>
       </c>
-      <c r="AW5" s="44" t="n"/>
       <c r="AX5" s="44" t="n"/>
+      <c r="AY5" s="44" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="29" t="inlineStr">
@@ -2822,7 +2844,7 @@
         <v/>
       </c>
       <c r="AL6" s="34">
-        <f>IF(OR(AG6="",R6=0),"",MIN(IF(AS6="",9.9E+99,AS6),FLOOR(AK6/R6,1)))</f>
+        <f>IF(OR(AG6="",R6=0),"",MIN(IF(AT6="",9.9E+99,AT6),FLOOR(AK6/R6,1)))</f>
         <v/>
       </c>
       <c r="AM6" s="38">
@@ -2830,7 +2852,7 @@
         <v/>
       </c>
       <c r="AN6" s="36">
-        <f>IF(OR(AG6="",R6=0),"",MIN(IF(AS6="",9.9E+99,AS6),AK6/R6))</f>
+        <f>IF(OR(AG6="",R6=0),"",MIN(IF(AT6="",9.9E+99,AT6),AK6/R6))</f>
         <v/>
       </c>
       <c r="AO6" s="38">
@@ -2838,23 +2860,28 @@
         <v/>
       </c>
       <c r="AP6" s="40" t="n"/>
-      <c r="AQ6" s="41" t="n"/>
+      <c r="AQ6" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
       <c r="AR6" s="41" t="n"/>
-      <c r="AS6" s="42" t="n"/>
-      <c r="AT6" s="43">
+      <c r="AS6" s="41" t="n"/>
+      <c r="AT6" s="42" t="n"/>
+      <c r="AU6" s="43">
         <f>IF(((S6*pax_cap*load_thin*ROUND(K6*L6*revleg_thin,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_thin,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6))&lt;=0,"",VLOOKUP(B6,country_opex,7,FALSE)/((S6*pax_cap*load_thin*ROUND(K6*L6*revleg_thin,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_thin,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6)))</f>
         <v/>
       </c>
-      <c r="AU6" s="43">
+      <c r="AV6" s="43">
         <f>IF(((S6*pax_cap*load_mid*ROUND(K6*L6*revleg_mid,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_mid,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6))&lt;=0,"",VLOOKUP(B6,country_opex,7,FALSE)/((S6*pax_cap*load_mid*ROUND(K6*L6*revleg_mid,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_mid,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6)))</f>
         <v/>
       </c>
-      <c r="AV6" s="43">
+      <c r="AW6" s="43">
         <f>IF(((S6*pax_cap*load_full*ROUND(K6*L6*revleg_full,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_full,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6))&lt;=0,"",VLOOKUP(B6,country_opex,7,FALSE)/((S6*pax_cap*load_full*ROUND(K6*L6*revleg_full,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_full,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6)))</f>
         <v/>
       </c>
-      <c r="AW6" s="44" t="n"/>
       <c r="AX6" s="44" t="n"/>
+      <c r="AY6" s="44" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="29" t="inlineStr">
@@ -2990,7 +3017,7 @@
         <v/>
       </c>
       <c r="AL7" s="34">
-        <f>IF(OR(AG7="",R7=0),"",MIN(IF(AS7="",9.9E+99,AS7),FLOOR(AK7/R7,1)))</f>
+        <f>IF(OR(AG7="",R7=0),"",MIN(IF(AT7="",9.9E+99,AT7),FLOOR(AK7/R7,1)))</f>
         <v/>
       </c>
       <c r="AM7" s="38">
@@ -2998,7 +3025,7 @@
         <v/>
       </c>
       <c r="AN7" s="36">
-        <f>IF(OR(AG7="",R7=0),"",MIN(IF(AS7="",9.9E+99,AS7),AK7/R7))</f>
+        <f>IF(OR(AG7="",R7=0),"",MIN(IF(AT7="",9.9E+99,AT7),AK7/R7))</f>
         <v/>
       </c>
       <c r="AO7" s="38">
@@ -3006,23 +3033,28 @@
         <v/>
       </c>
       <c r="AP7" s="40" t="n"/>
-      <c r="AQ7" s="41" t="n"/>
+      <c r="AQ7" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
       <c r="AR7" s="41" t="n"/>
-      <c r="AS7" s="42" t="n"/>
-      <c r="AT7" s="43">
+      <c r="AS7" s="41" t="n"/>
+      <c r="AT7" s="42" t="n"/>
+      <c r="AU7" s="43">
         <f>IF(((S7*pax_cap*load_thin*ROUND(K7*L7*revleg_thin,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_thin,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7))&lt;=0,"",VLOOKUP(B7,country_opex,7,FALSE)/((S7*pax_cap*load_thin*ROUND(K7*L7*revleg_thin,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_thin,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7)))</f>
         <v/>
       </c>
-      <c r="AU7" s="43">
+      <c r="AV7" s="43">
         <f>IF(((S7*pax_cap*load_mid*ROUND(K7*L7*revleg_mid,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_mid,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7))&lt;=0,"",VLOOKUP(B7,country_opex,7,FALSE)/((S7*pax_cap*load_mid*ROUND(K7*L7*revleg_mid,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_mid,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7)))</f>
         <v/>
       </c>
-      <c r="AV7" s="43">
+      <c r="AW7" s="43">
         <f>IF(((S7*pax_cap*load_full*ROUND(K7*L7*revleg_full,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_full,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7))&lt;=0,"",VLOOKUP(B7,country_opex,7,FALSE)/((S7*pax_cap*load_full*ROUND(K7*L7*revleg_full,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_full,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7)))</f>
         <v/>
       </c>
-      <c r="AW7" s="44" t="n"/>
       <c r="AX7" s="44" t="n"/>
+      <c r="AY7" s="44" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="29" t="inlineStr">
@@ -3160,7 +3192,7 @@
         <v/>
       </c>
       <c r="AL8" s="34">
-        <f>IF(OR(AG8="",R8=0),"",MIN(IF(AS8="",9.9E+99,AS8),FLOOR(AK8/R8,1)))</f>
+        <f>IF(OR(AG8="",R8=0),"",MIN(IF(AT8="",9.9E+99,AT8),FLOOR(AK8/R8,1)))</f>
         <v/>
       </c>
       <c r="AM8" s="38">
@@ -3168,7 +3200,7 @@
         <v/>
       </c>
       <c r="AN8" s="36">
-        <f>IF(OR(AG8="",R8=0),"",MIN(IF(AS8="",9.9E+99,AS8),AK8/R8))</f>
+        <f>IF(OR(AG8="",R8=0),"",MIN(IF(AT8="",9.9E+99,AT8),AK8/R8))</f>
         <v/>
       </c>
       <c r="AO8" s="38">
@@ -3176,23 +3208,28 @@
         <v/>
       </c>
       <c r="AP8" s="40" t="n"/>
-      <c r="AQ8" s="41" t="n"/>
+      <c r="AQ8" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
       <c r="AR8" s="41" t="n"/>
-      <c r="AS8" s="42" t="n"/>
-      <c r="AT8" s="43">
+      <c r="AS8" s="41" t="n"/>
+      <c r="AT8" s="42" t="n"/>
+      <c r="AU8" s="43">
         <f>IF(((S8*pax_cap*load_thin*ROUND(K8*L8*revleg_thin,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_thin,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8))&lt;=0,"",VLOOKUP(B8,country_opex,7,FALSE)/((S8*pax_cap*load_thin*ROUND(K8*L8*revleg_thin,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_thin,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8)))</f>
         <v/>
       </c>
-      <c r="AU8" s="43">
+      <c r="AV8" s="43">
         <f>IF(((S8*pax_cap*load_mid*ROUND(K8*L8*revleg_mid,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_mid,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8))&lt;=0,"",VLOOKUP(B8,country_opex,7,FALSE)/((S8*pax_cap*load_mid*ROUND(K8*L8*revleg_mid,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_mid,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8)))</f>
         <v/>
       </c>
-      <c r="AV8" s="43">
+      <c r="AW8" s="43">
         <f>IF(((S8*pax_cap*load_full*ROUND(K8*L8*revleg_full,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_full,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8))&lt;=0,"",VLOOKUP(B8,country_opex,7,FALSE)/((S8*pax_cap*load_full*ROUND(K8*L8*revleg_full,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_full,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8)))</f>
         <v/>
       </c>
-      <c r="AW8" s="44" t="n"/>
       <c r="AX8" s="44" t="n"/>
+      <c r="AY8" s="44" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="45" t="inlineStr">
@@ -3272,11 +3309,11 @@
         </is>
       </c>
       <c r="D13" s="49">
-        <f>SUMIFS(AL4:AL8,A4:A8,"Caribbean Mobility",AP4:AP8,"=",AQ4:AQ8,"=",AR4:AR8,"=")</f>
+        <f>SUMIFS(AL4:AL8,A4:A8,"Caribbean Mobility",AP4:AP8,"=",AQ4:AQ8,"Grounded")</f>
         <v/>
       </c>
       <c r="E13" s="50">
-        <f>SUMIFS(AM4:AM8,A4:A8,"Caribbean Mobility",AP4:AP8,"=",AQ4:AQ8,"=",AR4:AR8,"=")</f>
+        <f>SUMIFS(AM4:AM8,A4:A8,"Caribbean Mobility",AP4:AP8,"=",AQ4:AQ8,"Grounded")</f>
         <v/>
       </c>
     </row>
@@ -3292,6 +3329,21 @@
       </c>
       <c r="E14" s="46">
         <f>SUM(E13:E13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>ESTIMATED DEMAND (country-median cascade; held OUT of grounded floor)</t>
+        </is>
+      </c>
+      <c r="D15" s="51">
+        <f>SUMIF(AQ4:AQ8,"Estimated",AL4:AL8)</f>
+        <v/>
+      </c>
+      <c r="E15" s="52">
+        <f>SUMIF(AQ4:AQ8,"Estimated",AM4:AM8)</f>
         <v/>
       </c>
     </row>
@@ -3521,7 +3573,7 @@
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Live sum of grounded corridor market-rev (10% capture, today's demand, sourced corridors).</t>
+          <t>Live sum of grounded-floor corridor market-rev only (Floor bucket = Grounded; cascade-estimated rows held out). Matches growth.py _headline_anchor and deck TAM.</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3762,12 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="51" t="inlineStr">
+      <c r="A26" s="53" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="B26" s="52" t="inlineStr">
+      <c r="B26" s="54" t="inlineStr">
         <is>
           <t>All rungs are one multiplication chain off M_today, which is live off the corridor floor. Change any input (a fare, a multiplier, the scenario) and the whole ladder moves. Bands (low/MID/high) are never single points; greenfield census is per-partner.</t>
         </is>
